--- a/artfynd/A 41457-2025 artfynd.xlsx
+++ b/artfynd/A 41457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129703751</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129706300</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129706221</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129703721</v>
       </c>
       <c r="B5" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41457-2025 artfynd.xlsx
+++ b/artfynd/A 41457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129703751</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129706300</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129706221</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129703721</v>
       </c>
       <c r="B5" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41457-2025 artfynd.xlsx
+++ b/artfynd/A 41457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129703751</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129706300</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129706221</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129703721</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41457-2025 artfynd.xlsx
+++ b/artfynd/A 41457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129703751</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129706300</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129706221</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129703721</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41457-2025 artfynd.xlsx
+++ b/artfynd/A 41457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129703751</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129706300</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129706221</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129703721</v>
       </c>
       <c r="B5" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41457-2025 artfynd.xlsx
+++ b/artfynd/A 41457-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129703751</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129706300</v>
       </c>
       <c r="B3" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129706221</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129703721</v>
       </c>
       <c r="B5" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 41457-2025 artfynd.xlsx
+++ b/artfynd/A 41457-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129703751</v>
+        <v>129703721</v>
       </c>
       <c r="B2" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,7 +713,7 @@
         <v>501699</v>
       </c>
       <c r="R2" t="n">
-        <v>6844391</v>
+        <v>6844364</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,14 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129706300</v>
+        <v>129703751</v>
       </c>
       <c r="B3" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501567</v>
+        <v>501699</v>
       </c>
       <c r="R3" t="n">
-        <v>6844472</v>
+        <v>6844391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,11 +877,11 @@
         <v>129706221</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -971,14 +971,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129703721</v>
+        <v>129706300</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501699</v>
+        <v>501567</v>
       </c>
       <c r="R5" t="n">
-        <v>6844364</v>
+        <v>6844472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 41457-2025 artfynd.xlsx
+++ b/artfynd/A 41457-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129703721</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129703751</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129706221</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,8 +1085,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129706300</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>